--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104650_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104650_W22.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2409</v>
+        <v>8.2653</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9763</v>
+        <v>7.0057</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2646</v>
+        <v>1.2596</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4935</v>
+        <v>4.494</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6147</v>
+        <v>1.6114</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8788</v>
+        <v>2.8826</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1275</v>
+        <v>4.1024</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1719</v>
+        <v>3.1651</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3661</v>
+        <v>0.3916</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4278</v>
+        <v>0.4542</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6635</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2356</v>
+        <v>-0.2702</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6598</v>
+        <v>3.8401</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9952</v>
+        <v>2.6128</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6646</v>
+        <v>1.2272</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5418</v>
+        <v>3.5486</v>
       </c>
       <c r="H3" t="n">
         <v>2.9927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5492</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0684</v>
+        <v>4.0465</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5385</v>
+        <v>2.5198</v>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>1.5267</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5266</v>
+        <v>-0.4979</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4542</v>
+        <v>0.4729</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7304</v>
+        <v>-0.094</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0998</v>
+        <v>-0.4533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8302</v>
+        <v>0.3594</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8337</v>
+        <v>2.8902</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4329</v>
+        <v>1.1851</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4008</v>
+        <v>1.7051</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.3049</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3245</v>
+        <v>0.3354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9755</v>
+        <v>0.9695</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0458</v>
+        <v>1.032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4051</v>
+        <v>0.3943</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2542</v>
+        <v>0.2729</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0541</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3871</v>
+        <v>0.1531</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4413</v>
+        <v>-0.1612</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6173</v>
+        <v>2.5539</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3078</v>
+        <v>2.2847</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3096</v>
+        <v>0.2691</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1177</v>
+        <v>2.1149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7157</v>
+        <v>0.7179</v>
       </c>
       <c r="I5" t="n">
-        <v>1.402</v>
+        <v>1.397</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0548</v>
+        <v>3.033</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3782</v>
+        <v>1.365</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9371</v>
+        <v>-0.918</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4077</v>
+        <v>-0.4716</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.747</v>
+        <v>-0.7482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3393</v>
+        <v>0.2766</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3359</v>
+        <v>2.2613</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0496</v>
+        <v>2.6721</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7138</v>
+        <v>-0.4108</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6251</v>
+        <v>1.6143</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4272</v>
+        <v>-0.4197</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0523</v>
+        <v>2.034</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7172</v>
+        <v>2.6861</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L6" t="n">
-        <v>3.3477</v>
+        <v>3.3206</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0921</v>
+        <v>-1.0719</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3819</v>
+        <v>-0.4425</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6261</v>
+        <v>0.0346</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7558</v>
+        <v>-0.4771</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0043</v>
+        <v>1.1074</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6152</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3891</v>
+        <v>0.4234</v>
       </c>
       <c r="G7" t="n">
-        <v>1.053</v>
+        <v>1.0551</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2755</v>
+        <v>-0.1754</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0181</v>
+        <v>0.0882</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9113</v>
+        <v>0.9775</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0146</v>
+        <v>0.3924</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8966</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9998</v>
+        <v>3.9913</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6116</v>
+        <v>1.6221</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3882</v>
+        <v>2.3691</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3959</v>
+        <v>3.3589</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2051</v>
+        <v>1.1926</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1909</v>
+        <v>2.1663</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6038</v>
+        <v>0.6324</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4065</v>
+        <v>0.4296</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8617</v>
+        <v>-0.7861</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.113</v>
+        <v>-0.6902</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2513</v>
+        <v>-0.0959</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5516</v>
+        <v>0.9697</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8612</v>
+        <v>1.1834</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3095</v>
+        <v>-0.2137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.894</v>
+        <v>0.8953</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5819</v>
       </c>
       <c r="I9" t="n">
-        <v>0.333</v>
+        <v>0.3134</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8864</v>
+        <v>1.8551</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0044</v>
+        <v>0.9997</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8821</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.9598</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4434</v>
+        <v>-0.4179</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7034</v>
+        <v>-1.2915</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0253</v>
+        <v>-0.6717</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6781</v>
+        <v>-0.6198</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5209</v>
+        <v>0.5896</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4673</v>
+        <v>0.5343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0537</v>
+        <v>0.0553</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6782</v>
+        <v>0.6778</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6782</v>
+        <v>0.6778</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3841</v>
+        <v>-0.3159</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1441</v>
+        <v>-0.0717</v>
       </c>
       <c r="E11" t="n">
-        <v>0.552</v>
+        <v>0.5421</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.6138</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2777</v>
+        <v>0.2815</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1312</v>
+        <v>0.1402</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1466</v>
+        <v>0.1413</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3221</v>
+        <v>0.3101</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0444</v>
+        <v>-0.0285</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0097</v>
+        <v>0.0534</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2299</v>
+        <v>0.232</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8913</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1564</v>
+        <v>-0.2071</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7349</v>
+        <v>-0.5555</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1069</v>
+        <v>0.1167</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6573</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5437</v>
+        <v>-0.5406</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4559</v>
+        <v>-0.46</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5251</v>
+        <v>-0.529</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5628</v>
+        <v>0.5768</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5814</v>
+        <v>0.5884</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2798</v>
+        <v>0.3891</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2994</v>
+        <v>0.253</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6156</v>
+        <v>-5.2493</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1292</v>
+        <v>-4.8188</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4864</v>
+        <v>-0.4306</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8268</v>
+        <v>-2.8372</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9768</v>
+        <v>-0.9792</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8499</v>
+        <v>-1.8579</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.887</v>
+        <v>-1.922</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6625</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2423</v>
+        <v>-1.2595</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9398</v>
+        <v>-0.9152</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.201</v>
+        <v>-0.8188</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2271</v>
+        <v>-0.1983</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.0247</v>
+        <v>17.3714</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9865</v>
+        <v>14.07070000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.038299999999999</v>
+        <v>3.3005</v>
       </c>
       <c r="G14" t="n">
-        <v>17.2609</v>
+        <v>17.2572</v>
       </c>
       <c r="H14" t="n">
-        <v>8.3322</v>
+        <v>8.397099999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>8.9291</v>
+        <v>8.860099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>19.4091</v>
+        <v>19.1722</v>
       </c>
       <c r="K14" t="n">
-        <v>7.642100000000001</v>
+        <v>7.544499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>11.7673</v>
+        <v>11.6276</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1482</v>
+        <v>-1.9148</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8527</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8381</v>
+        <v>-2.767600000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5365</v>
+        <v>4.552499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.805</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.841100000000001</v>
+        <v>-3.507300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0567</v>
+        <v>-1.6987</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7845</v>
+        <v>-1.8085</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9320000000000002</v>
+        <v>-0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.370699999999999</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3598</v>
+        <v>2.2826</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1876</v>
+        <v>2.8621</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8278</v>
+        <v>-0.5795</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.437</v>
+        <v>-0.4444</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0983</v>
+        <v>1.0836</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5353</v>
+        <v>-1.528</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6333</v>
+        <v>1.601</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0118</v>
+        <v>1.9887</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0702</v>
+        <v>-2.0455</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2032</v>
+        <v>0.727</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5383</v>
+        <v>0.1716</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3351</v>
+        <v>0.5554</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0936</v>
+        <v>0.5738</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3483</v>
+        <v>2.1136</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2547</v>
+        <v>-1.5398</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2864</v>
+        <v>-2.4193</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4517</v>
+        <v>0.3825</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1653</v>
+        <v>-2.8017</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5358</v>
+        <v>0.4274</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7202</v>
+        <v>0.9718</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8156</v>
+        <v>-0.5443</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2494</v>
+        <v>-2.8467</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2685</v>
+        <v>-0.5893</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9808</v>
+        <v>-2.2574</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2609</v>
+        <v>1.2694</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9467</v>
+        <v>0.6454</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3142</v>
+        <v>0.624</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.407</v>
+        <v>0.4153</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9161</v>
+        <v>0.617</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5091</v>
+        <v>-0.2017</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4156</v>
+        <v>0.284</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3912</v>
+        <v>0.451</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8068</v>
+        <v>-0.1669</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4596</v>
+        <v>1.5138</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9902</v>
+        <v>0.71</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5306</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8752</v>
+        <v>-1.2298</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.599</v>
+        <v>-0.259</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2762</v>
+        <v>-0.9708</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0909</v>
+        <v>0.5865</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4053</v>
+        <v>0.2413</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6856</v>
+        <v>0.3452</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0919</v>
+        <v>0.2374</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3399</v>
+        <v>1.5538</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4318</v>
+        <v>-1.3164</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0741</v>
+        <v>1.0828</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8528</v>
+        <v>0.853</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2213</v>
+        <v>0.2298</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2112</v>
+        <v>3.2008</v>
       </c>
       <c r="K18" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1371</v>
+        <v>-2.118</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6708</v>
+        <v>-0.3414</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0248</v>
+        <v>0.1187</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.64</v>
+        <v>-1.1752</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5854</v>
+        <v>-0.4371</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2254</v>
+        <v>-0.7381</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5056</v>
+        <v>0.0629</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0765</v>
+        <v>0.5111</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4291</v>
+        <v>-0.4482</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5461</v>
+        <v>0.6061</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.163</v>
+        <v>0.5688</v>
       </c>
       <c r="L19" t="n">
-        <v>0.709</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0516</v>
+        <v>-0.5432</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9135</v>
+        <v>-0.0578</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1381</v>
+        <v>-0.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9998</v>
+        <v>-0.3276</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1735</v>
+        <v>0.095</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8263</v>
+        <v>-0.4226</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6583</v>
+        <v>-1.505</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7855</v>
+        <v>1.2883</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8728</v>
+        <v>-2.7933</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0548</v>
+        <v>-1.83</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5079</v>
+        <v>-1.5308</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4531</v>
+        <v>-0.2992</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6088</v>
+        <v>0.7614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5715</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.8411</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.554</v>
+        <v>-2.5915</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>-1.4511</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>-1.1403</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8057</v>
+        <v>0.7316</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2601</v>
+        <v>0.5269</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5456</v>
+        <v>0.2047</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8865</v>
+        <v>-1.7139</v>
       </c>
       <c r="E21" t="n">
-        <v>1.192</v>
+        <v>-0.1309</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0785</v>
+        <v>-1.583</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8348</v>
+        <v>-1.4955</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.531</v>
+        <v>-1.0743</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3038</v>
+        <v>-0.4212</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7867</v>
+        <v>0.5384</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.1691</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8529</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6215</v>
+        <v>-2.0339</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4648</v>
+        <v>-0.9052</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1567</v>
+        <v>-1.1287</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3605</v>
+        <v>0.9198</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4053</v>
+        <v>0.4689</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0448</v>
+        <v>0.4509</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.711</v>
+        <v>-2.4971</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6839</v>
+        <v>-1.716</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.027</v>
+        <v>-0.7811</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8434</v>
+        <v>-1.8503</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9954</v>
+        <v>-2.007</v>
       </c>
       <c r="I22" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4318</v>
+        <v>-0.4614</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8769</v>
+        <v>-0.9005</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4116</v>
+        <v>-1.389</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2531</v>
+        <v>-0.0338</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1179</v>
+        <v>-0.1165</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1352</v>
+        <v>0.0827</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.26</v>
+        <v>-3.5291</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4438</v>
+        <v>-2.7243</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8162</v>
+        <v>-0.8048</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4421</v>
+        <v>-3.3467</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5337</v>
+        <v>-2.8599</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9085</v>
+        <v>-0.4867</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1818</v>
+        <v>-1.5301</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4701</v>
+        <v>-1.9692</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>0.4392</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2603</v>
+        <v>-1.8166</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.8907</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1967</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.048</v>
+        <v>0.0452</v>
       </c>
       <c r="T23" t="n">
-        <v>0.738</v>
+        <v>-0.0561</v>
       </c>
       <c r="U23" t="n">
-        <v>0.31</v>
+        <v>0.1013</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7918</v>
+        <v>-3.9638</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4612</v>
+        <v>-3.1693</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3306</v>
+        <v>-0.7945</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3439</v>
+        <v>-4.4445</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8482</v>
+        <v>-2.5441</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4957</v>
+        <v>-1.9004</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5055</v>
+        <v>-3.2015</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9506</v>
+        <v>-2.4863</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4451</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8384</v>
+        <v>-1.243</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8976</v>
+        <v>-0.0578</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9408</v>
+        <v>-1.1852</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2211</v>
+        <v>0.3425</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1785</v>
+        <v>0.0322</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3995</v>
+        <v>0.3104</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8457</v>
+        <v>-5.3581</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.233</v>
+        <v>-3.5577</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6127</v>
+        <v>-1.8004</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8538</v>
+        <v>-2.8564</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6491</v>
+        <v>-1.6622</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2047</v>
+        <v>-1.1942</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.514</v>
+        <v>-1.5412</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8769</v>
+        <v>-0.9005</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3398</v>
+        <v>-1.3152</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>0.235</v>
+        <v>0.7259</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4506</v>
+        <v>0.2598</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6856</v>
+        <v>0.4661</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.0248</v>
+        <v>-16.2331</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0381</v>
+        <v>-3.3005</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.9866</v>
+        <v>-12.9326</v>
       </c>
       <c r="G26" t="n">
-        <v>-17.2609</v>
+        <v>-17.2574</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.332000000000001</v>
+        <v>-8.3971</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.929</v>
+        <v>-8.860100000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>2.148400000000001</v>
+        <v>1.9147</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6900000000000002</v>
+        <v>-0.8525999999999997</v>
       </c>
       <c r="L26" t="n">
-        <v>2.8382</v>
+        <v>2.7676</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.4091</v>
+        <v>-19.1724</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.6419</v>
+        <v>-7.544600000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.767</v>
+        <v>-11.6277</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.536700000000001</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3418</v>
+        <v>-11.3818</v>
       </c>
       <c r="R26" t="n">
-        <v>6.804900000000001</v>
+        <v>6.8289</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8412</v>
+        <v>4.6451</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7848</v>
+        <v>1.8084</v>
       </c>
       <c r="U26" t="n">
-        <v>2.0565</v>
+        <v>2.8368</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9319999999999993</v>
+        <v>0.9317</v>
       </c>
       <c r="W26" t="n">
-        <v>4.370699999999999</v>
+        <v>4.3579</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104650_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104650_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104650_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
